--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_37.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2388763.252814191</v>
+        <v>2389877.075800647</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14707975.22838743</v>
+        <v>14705061.84708724</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14707975.22838743</v>
+        <v>14705061.84708724</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>664579.1640370116</v>
+        <v>663366.9320941061</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>664579.1640370116</v>
+        <v>663366.9320941061</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29399722.56894159</v>
+        <v>29401887.05800694</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>81.99931295557205</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -666,16 +666,16 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>6.688316575840815</v>
       </c>
       <c r="G2" t="n">
-        <v>1.265209903585474</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>9.812950452214863e-13</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S3" t="n">
-        <v>128.1398644816394</v>
+        <v>374</v>
       </c>
       <c r="T3" t="n">
-        <v>373</v>
+        <v>278.6487531723254</v>
       </c>
       <c r="U3" t="n">
-        <v>373</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -912,7 +912,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>83.42203556964708</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
         <v>184.8805867536895</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>171.4288988569895</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>373.0000000000002</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
@@ -1033,13 +1033,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>339.8430061141969</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80.07191941636793</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S8" t="n">
         <v>85.41253966161941</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>94.60970577102681</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>373.0000000000004</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>167.7225441899962</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
         <v>4.464774651476091</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1380,10 +1380,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H11" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>137.6511320520606</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T11" t="n">
         <v>261.2171194170061</v>
@@ -1434,7 +1434,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>192.3174326828064</v>
+        <v>187.7405476863115</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>288.4988294066018</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>243.5785150981524</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,19 +1492,19 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.2619859716246</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U12" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V12" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
         <v>113.3731429098285</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.305168319656873</v>
+        <v>3.305168319656647</v>
       </c>
       <c r="M13" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N13" t="n">
         <v>150.9111244520127</v>
@@ -1571,10 +1571,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S13" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>78.70511040610097</v>
+        <v>78.70511040609921</v>
       </c>
       <c r="H14" t="n">
         <v>73.89995518593946</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288.4988294066023</v>
+        <v>288.4988294066018</v>
       </c>
       <c r="C15" t="n">
         <v>42.09991244551929</v>
@@ -1690,7 +1690,7 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F15" t="n">
         <v>20.63624233787687</v>
@@ -1738,19 +1738,19 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U15" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.305168319656647</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M16" t="n">
         <v>97.89093927140237</v>
@@ -1802,7 +1802,7 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P16" t="n">
-        <v>288.4057989676218</v>
+        <v>285.555437490155</v>
       </c>
       <c r="Q16" t="n">
         <v>351.422266425598</v>
@@ -1854,7 +1854,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>78.70511040610097</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H17" t="n">
         <v>73.89995518593946</v>
@@ -1905,7 +1905,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>273.2818334606677</v>
+        <v>268.7049484641728</v>
       </c>
       <c r="Y17" t="n">
         <v>192.3174326828064</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066019</v>
       </c>
       <c r="C18" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -1972,16 +1972,16 @@
         <v>132.901311285366</v>
       </c>
       <c r="T18" t="n">
-        <v>306.1182172230725</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U18" t="n">
         <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>100.8627394453875</v>
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>28.98969199588053</v>
+        <v>28.98969199588057</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         <v>85.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>81.31274371151873</v>
+        <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.2280170485541</v>
+        <v>137.6511320520588</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2164,16 +2164,16 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612264</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,25 +2203,25 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S21" t="n">
-        <v>132.901311285366</v>
+        <v>355.8435840456414</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279685</v>
+        <v>402.1759444627968</v>
       </c>
       <c r="U21" t="n">
-        <v>400.1584257979226</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>323.8050122056632</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>80.39139276613435</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M22" t="n">
-        <v>95.04057779393561</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588096</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2367,13 +2367,13 @@
         <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
-        <v>261.2171194170061</v>
+        <v>256.6402344205115</v>
       </c>
       <c r="U23" t="n">
         <v>330.1032663978569</v>
       </c>
       <c r="V23" t="n">
-        <v>306.2741391703302</v>
+        <v>310.8510241668239</v>
       </c>
       <c r="W23" t="n">
         <v>319.3734759809475</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>265.042185205795</v>
+        <v>265.0421852057946</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H24" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T24" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
         <v>95.51066719152016</v>
@@ -2458,10 +2458,10 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3.305168319656873</v>
+        <v>3.305168319656647</v>
       </c>
       <c r="M25" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N25" t="n">
         <v>150.9111244520127</v>
@@ -2519,10 +2519,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>78.70511040609921</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>142.2280170485541</v>
+        <v>137.6511320520588</v>
       </c>
       <c r="T26" t="n">
         <v>261.2171194170061</v>
@@ -2644,10 +2644,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S27" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U27" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V27" t="n">
         <v>95.51066719152016</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319656647</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2756,10 +2756,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S28" t="n">
-        <v>31.84005347334727</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,10 +2844,10 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U29" t="n">
-        <v>325.5263814013622</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V29" t="n">
-        <v>310.8510241668239</v>
+        <v>306.2741391703298</v>
       </c>
       <c r="W29" t="n">
         <v>319.3734759809475</v>
@@ -2869,22 +2869,22 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>42.09991244551929</v>
+        <v>265.0421852057946</v>
       </c>
       <c r="D30" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,25 +2914,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>304.1006985581978</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>80.39139276613435</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
-        <v>148.0607629745462</v>
+        <v>150.9111244520127</v>
       </c>
       <c r="O31" t="n">
         <v>227.9026788331133</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364713</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>83.28199540259411</v>
+        <v>78.70511040609918</v>
       </c>
       <c r="H32" t="n">
         <v>73.89995518593948</v>
@@ -3084,7 +3084,7 @@
         <v>330.1032663978569</v>
       </c>
       <c r="V32" t="n">
-        <v>306.2741391703289</v>
+        <v>310.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>319.3734759809475</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>265.0421852057946</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>28.93768689770263</v>
@@ -3163,13 +3163,13 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V33" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517954</v>
       </c>
       <c r="W33" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>64.22801704855405</v>
+        <v>60.92708723799848</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
       </c>
       <c r="U35" t="n">
-        <v>248.8023365873013</v>
+        <v>252.1032663978569</v>
       </c>
       <c r="V35" t="n">
         <v>232.8510241668239</v>
@@ -3346,22 +3346,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>106.2240344705043</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3391,10 +3391,10 @@
         <v>101.2619859716246</v>
       </c>
       <c r="S36" t="n">
-        <v>260.9910971358505</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T36" t="n">
-        <v>374.0000000000002</v>
+        <v>5.175944462796835</v>
       </c>
       <c r="U36" t="n">
         <v>3.158425797922597</v>
@@ -3409,7 +3409,7 @@
         <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>374.0000000000002</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="37">
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3564,7 +3564,7 @@
         <v>241.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>195.2818334606677</v>
+        <v>191.9809036501121</v>
       </c>
       <c r="Y38" t="n">
         <v>114.3174326828064</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>308.6385478666184</v>
+        <v>374</v>
       </c>
       <c r="S39" t="n">
-        <v>374.000000000002</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796835</v>
+        <v>374</v>
       </c>
       <c r="U39" t="n">
         <v>3.158425797922597</v>
@@ -3646,7 +3646,7 @@
         <v>22.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.391392766134345</v>
+        <v>229.9766710320982</v>
       </c>
     </row>
     <row r="40">
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>125.8743140373655</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>356.1032663978569</v>
+        <v>313.4382881485668</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
@@ -3801,7 +3801,7 @@
         <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>68.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>57.32446034312783</v>
+        <v>54.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>49.67209722191262</v>
@@ -3829,10 +3829,10 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861225</v>
+        <v>31.95013964861226</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604377</v>
+        <v>33.93095497146885</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>205.2619859716246</v>
+        <v>205.2619859716245</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712344</v>
+        <v>32.15552979712345</v>
       </c>
       <c r="M43" t="n">
         <v>123.8909392714024</v>
@@ -3932,19 +3932,19 @@
         <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>253.9026788331133</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>220.5354044354171</v>
+        <v>374</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>42.5980297951833</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334727</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>16.16097105909921</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
-        <v>113.8095999937037</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>356.1032663978569</v>
@@ -4038,7 +4038,7 @@
         <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>123.8909392714024</v>
+        <v>2.581873503942997</v>
       </c>
       <c r="N46" t="n">
         <v>176.9111244520127</v>
@@ -4175,7 +4175,7 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>252.6909342325405</v>
+        <v>374</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.731003807232</v>
+        <v>108.7310038072345</v>
       </c>
       <c r="C2" t="n">
-        <v>54.7566823496624</v>
+        <v>58.75668234966486</v>
       </c>
       <c r="D2" t="n">
-        <v>44.31309069324847</v>
+        <v>48.31309069325093</v>
       </c>
       <c r="E2" t="n">
-        <v>39.90572745398721</v>
+        <v>43.90572745398968</v>
       </c>
       <c r="F2" t="n">
-        <v>34.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>33.68871875540405</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>29.84000000000099</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>399.11</v>
+        <v>263.0661931588676</v>
       </c>
       <c r="L2" t="n">
-        <v>768.3799999999999</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M2" t="n">
-        <v>1064.638108133742</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>1064.638108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1064.638108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1122.73</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1405.632174038565</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1218.884106610596</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>967.1785586019998</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>735.0058069183393</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>494.2245180486953</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>300.0004438460006</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>187.5585926512467</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="C3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="D3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="E3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="F3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="G3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="H3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
-        <v>29.84</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>173.6113405614803</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>397.8775591086939</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>716.3885386284223</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>857.5031803712816</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1047.274153846774</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.994549492757</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1492</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1356.997993968056</v>
+        <v>971.6833037965423</v>
       </c>
       <c r="S3" t="n">
-        <v>1227.563787420946</v>
+        <v>593.9055260187645</v>
       </c>
       <c r="T3" t="n">
-        <v>850.7961106532689</v>
+        <v>312.4421389760115</v>
       </c>
       <c r="U3" t="n">
-        <v>474.0284338855921</v>
+        <v>312.2442341296251</v>
       </c>
       <c r="V3" t="n">
-        <v>459.371194298198</v>
+        <v>297.586994542231</v>
       </c>
       <c r="W3" t="n">
-        <v>426.6710499448359</v>
+        <v>264.8868501888688</v>
       </c>
       <c r="X3" t="n">
-        <v>406.6076767676768</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="Y3" t="n">
-        <v>29.84</v>
+        <v>244.8234770117097</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.84</v>
+        <v>458.0187904176125</v>
       </c>
       <c r="C4" t="n">
-        <v>29.84</v>
+        <v>584.0207962360482</v>
       </c>
       <c r="D4" t="n">
-        <v>88.58946781506729</v>
+        <v>584.0207962360482</v>
       </c>
       <c r="E4" t="n">
-        <v>206.4183720264803</v>
+        <v>701.8497004474613</v>
       </c>
       <c r="F4" t="n">
-        <v>330.7793446184158</v>
+        <v>701.8497004474613</v>
       </c>
       <c r="G4" t="n">
-        <v>484.3680055872683</v>
+        <v>855.4383614163137</v>
       </c>
       <c r="H4" t="n">
-        <v>655.503581566338</v>
+        <v>1026.573937395383</v>
       </c>
       <c r="I4" t="n">
-        <v>882.1125562401257</v>
+        <v>1026.573937395383</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.382556240126</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.903127881912</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.663548464727</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1293.937231267251</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.454310393385</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>932.8409073660641</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>664.9602361121326</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3872397226397</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.84</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>29.84</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>29.84</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V4" t="n">
-        <v>29.84</v>
+        <v>458.0187904176125</v>
       </c>
       <c r="W4" t="n">
-        <v>29.84</v>
+        <v>458.0187904176125</v>
       </c>
       <c r="X4" t="n">
-        <v>29.84</v>
+        <v>458.0187904176125</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.84</v>
+        <v>458.0187904176125</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.834147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.85982591751439</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.41623426110046</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.00887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.06985212485753</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.68871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.84</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>399.1100000000001</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>768.3800000000001</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1137.65</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>1137.65</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>1137.65</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>1137.65</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1195.741891866258</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.735317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1220.987250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.2817021698519</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1089504861914</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.3276616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1035874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6617362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>723.3956081758904</v>
+        <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>358.6482218672851</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
-        <v>358.6482218672851</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>358.6482218672851</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
-        <v>358.6482218672851</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.317370930016</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K6" t="n">
-        <v>398.5835894772296</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L6" t="n">
-        <v>717.0945689969581</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2092107398173</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N6" t="n">
-        <v>1047.274153846774</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1337.994549492757</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P6" t="n">
-        <v>1492</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1345.46108157432</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1172.300577678371</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>795.5329009106941</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>791.0142701401923</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>790.8163652938058</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>776.1591257064117</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>743.4589813530496</v>
+        <v>785.4755555555557</v>
       </c>
       <c r="X6" t="n">
-        <v>723.3956081758904</v>
+        <v>407.6977777777778</v>
       </c>
       <c r="Y6" t="n">
-        <v>723.3956081758904</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>88.58946781506707</v>
+        <v>91.43988839788217</v>
       </c>
       <c r="E7" t="n">
-        <v>206.4183720264801</v>
+        <v>209.2687926092952</v>
       </c>
       <c r="F7" t="n">
-        <v>330.7793446184156</v>
+        <v>333.6297652012307</v>
       </c>
       <c r="G7" t="n">
-        <v>484.368005587268</v>
+        <v>487.2184261700831</v>
       </c>
       <c r="H7" t="n">
-        <v>655.5035815663377</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I7" t="n">
-        <v>882.1125562401255</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.382556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.903127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.663548464727</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M7" t="n">
-        <v>1293.937231267251</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.454310393385</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O7" t="n">
-        <v>932.8409073660641</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P7" t="n">
-        <v>664.9602361121326</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3872397226397</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R7" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.26367574991085</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>88.58946781506707</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.7884999460191</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>56.8141784884495</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>46.37058683203557</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>41.96322359277431</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>37.02420469579264</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.64713203391644</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
-        <v>29.83999999999958</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>399.1100000000001</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>768.3800000000001</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1137.65</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M8" t="n">
-        <v>1137.65</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1137.65</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1137.65</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1196.314206388871</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1492.000000000002</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S8" t="n">
-        <v>1405.724707412507</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1218.994415731962</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>967.2891925799722</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>735.1164408963117</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>494.3351520266677</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>300.111077823973</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>187.6692266292191</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>727.4256405248639</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C9" t="n">
-        <v>727.4256405248639</v>
+        <v>29.92</v>
       </c>
       <c r="D9" t="n">
-        <v>375.9734315372855</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5185557413367</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>399.1286311753428</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>718.1019687139392</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>859.7561604567984</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1046.360878846775</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1337.587921002191</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1345.738421006376</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>968.9707442386994</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>799.5540329356729</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>795.0441595503436</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>794.8463976427793</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>780.1891580553852</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>747.489013702023</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>727.4256405248639</v>
+        <v>868.0105234510568</v>
       </c>
       <c r="Y9" t="n">
-        <v>727.4256405248639</v>
+        <v>490.2327456732789</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1250.627100357226</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C10" t="n">
-        <v>1376.629106175661</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D10" t="n">
-        <v>1385.387095409585</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E10" t="n">
-        <v>1385.387095409585</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F10" t="n">
-        <v>1385.387095409585</v>
+        <v>885.6284561163022</v>
       </c>
       <c r="G10" t="n">
-        <v>1385.387095409585</v>
+        <v>1039.218902331056</v>
       </c>
       <c r="H10" t="n">
-        <v>1385.387095409585</v>
+        <v>1210.370350769143</v>
       </c>
       <c r="I10" t="n">
-        <v>1385.387095409585</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1385.387095409585</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1385.387095409585</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1385.387095409585</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1292.946305617309</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.742122945132</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.3861797621563</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>664.7258098826245</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3053387456568</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.29478771712391</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1561373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>505.7173598420843</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>704.5387527280302</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>876.4296709877076</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>1027.460462011901</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>1138.869762690933</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>608.1266695820786</v>
+        <v>608.1266695820785</v>
       </c>
       <c r="C11" t="n">
-        <v>476.3341663063272</v>
+        <v>476.3341663063271</v>
       </c>
       <c r="D11" t="n">
-        <v>384.0723928317315</v>
+        <v>384.0723928317313</v>
       </c>
       <c r="E11" t="n">
-        <v>297.8468477742884</v>
+        <v>297.8468477742883</v>
       </c>
       <c r="F11" t="n">
-        <v>211.0896470591249</v>
+        <v>211.0896470591248</v>
       </c>
       <c r="G11" t="n">
-        <v>126.9664193797369</v>
+        <v>126.9664193797368</v>
       </c>
       <c r="H11" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I11" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J11" t="n">
-        <v>141.5959849731395</v>
+        <v>567.5976741934346</v>
       </c>
       <c r="K11" t="n">
-        <v>327.3927226113305</v>
+        <v>1215.057674193435</v>
       </c>
       <c r="L11" t="n">
-        <v>934.771587554808</v>
+        <v>1582.231587554807</v>
       </c>
       <c r="M11" t="n">
-        <v>1582.231587554808</v>
+        <v>1582.231587554807</v>
       </c>
       <c r="N11" t="n">
-        <v>2229.691587554809</v>
+        <v>2229.691587554807</v>
       </c>
       <c r="O11" t="n">
-        <v>2406.244759641281</v>
+        <v>2406.244759641279</v>
       </c>
       <c r="P11" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="Q11" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="R11" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="S11" t="n">
-        <v>2476.958452472668</v>
+        <v>2472.335336314592</v>
       </c>
       <c r="T11" t="n">
-        <v>2213.102776293874</v>
+        <v>2208.479660135798</v>
       </c>
       <c r="U11" t="n">
-        <v>1879.665133467756</v>
+        <v>1875.04201730968</v>
       </c>
       <c r="V11" t="n">
-        <v>1565.674199965913</v>
+        <v>1561.051083807838</v>
       </c>
       <c r="W11" t="n">
-        <v>1243.074729278087</v>
+        <v>1238.451613120012</v>
       </c>
       <c r="X11" t="n">
-        <v>967.0324732572109</v>
+        <v>962.4093570991351</v>
       </c>
       <c r="Y11" t="n">
-        <v>772.7724402442751</v>
+        <v>772.772440244275</v>
       </c>
     </row>
     <row r="12">
@@ -5087,34 +5087,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1050.080134179741</v>
+        <v>502.663697048149</v>
       </c>
       <c r="C12" t="n">
-        <v>685.3327478711351</v>
+        <v>460.1385329617659</v>
       </c>
       <c r="D12" t="n">
-        <v>333.8805388835567</v>
+        <v>430.9085461964096</v>
       </c>
       <c r="E12" t="n">
-        <v>309.9693295684934</v>
+        <v>84.77511465912414</v>
       </c>
       <c r="F12" t="n">
-        <v>63.93042542894551</v>
+        <v>63.93042542894548</v>
       </c>
       <c r="G12" t="n">
-        <v>57.92018335964021</v>
+        <v>57.92018335964016</v>
       </c>
       <c r="H12" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I12" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J12" t="n">
-        <v>250.111345930016</v>
+        <v>250.1113459300159</v>
       </c>
       <c r="K12" t="n">
-        <v>565.4996394772296</v>
+        <v>565.4996394772295</v>
       </c>
       <c r="L12" t="n">
         <v>1006.535493996958</v>
@@ -5129,34 +5129,34 @@
         <v>2052.148604861293</v>
       </c>
       <c r="P12" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="R12" t="n">
-        <v>2132.837892265885</v>
+        <v>1810.615670043662</v>
       </c>
       <c r="S12" t="n">
-        <v>1998.594143492788</v>
+        <v>1676.371921270565</v>
       </c>
       <c r="T12" t="n">
-        <v>1914.578037974811</v>
+        <v>1592.355815752589</v>
       </c>
       <c r="U12" t="n">
-        <v>1832.599830098122</v>
+        <v>1510.377607875899</v>
       </c>
       <c r="V12" t="n">
-        <v>1736.124408692546</v>
+        <v>1091.679964248101</v>
       </c>
       <c r="W12" t="n">
-        <v>1621.606082521002</v>
+        <v>977.1616380765568</v>
       </c>
       <c r="X12" t="n">
-        <v>1519.724527525661</v>
+        <v>875.2800830812158</v>
       </c>
       <c r="Y12" t="n">
-        <v>1438.521100489161</v>
+        <v>794.0766560447165</v>
       </c>
     </row>
     <row r="13">
@@ -5211,13 +5211,13 @@
         <v>821.1153191039225</v>
       </c>
       <c r="Q13" t="n">
-        <v>466.1433328154397</v>
+        <v>466.1433328154396</v>
       </c>
       <c r="R13" t="n">
         <v>84.48167017509826</v>
       </c>
       <c r="S13" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="T13" t="n">
         <v>163.0051070276573</v>
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>603.5035534240047</v>
+        <v>603.5035534240029</v>
       </c>
       <c r="C14" t="n">
-        <v>471.7110501482533</v>
+        <v>471.7110501482515</v>
       </c>
       <c r="D14" t="n">
-        <v>379.4492766736576</v>
+        <v>379.4492766736557</v>
       </c>
       <c r="E14" t="n">
-        <v>293.2237316162145</v>
+        <v>293.2237316162127</v>
       </c>
       <c r="F14" t="n">
-        <v>206.466530901051</v>
+        <v>206.4665309010492</v>
       </c>
       <c r="G14" t="n">
-        <v>126.9664193797369</v>
+        <v>126.9664193797368</v>
       </c>
       <c r="H14" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I14" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J14" t="n">
         <v>141.5959849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>327.3927226113305</v>
+        <v>789.0559849731395</v>
       </c>
       <c r="L14" t="n">
-        <v>557.8900049228882</v>
+        <v>1436.515984973139</v>
       </c>
       <c r="M14" t="n">
-        <v>1205.350004922889</v>
+        <v>2083.97598497314</v>
       </c>
       <c r="N14" t="n">
-        <v>1852.810004922889</v>
+        <v>2229.691587554807</v>
       </c>
       <c r="O14" t="n">
-        <v>2406.244759641281</v>
+        <v>2406.244759641279</v>
       </c>
       <c r="P14" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="Q14" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="R14" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="S14" t="n">
-        <v>2472.335336314594</v>
+        <v>2472.335336314592</v>
       </c>
       <c r="T14" t="n">
-        <v>2208.4796601358</v>
+        <v>2208.479660135798</v>
       </c>
       <c r="U14" t="n">
-        <v>1875.042017309682</v>
+        <v>1875.04201730968</v>
       </c>
       <c r="V14" t="n">
-        <v>1561.051083807839</v>
+        <v>1561.051083807838</v>
       </c>
       <c r="W14" t="n">
-        <v>1238.451613120013</v>
+        <v>1238.451613120012</v>
       </c>
       <c r="X14" t="n">
-        <v>962.409357099137</v>
+        <v>962.4093570991351</v>
       </c>
       <c r="Y14" t="n">
-        <v>768.1493240862012</v>
+        <v>768.1493240861994</v>
       </c>
     </row>
     <row r="15">
@@ -5324,34 +5324,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502.6636970481491</v>
+        <v>180.4414748259267</v>
       </c>
       <c r="C15" t="n">
-        <v>460.1385329617659</v>
+        <v>137.9163107395436</v>
       </c>
       <c r="D15" t="n">
-        <v>430.9085461964097</v>
+        <v>108.6863239741874</v>
       </c>
       <c r="E15" t="n">
-        <v>84.77511465912417</v>
+        <v>84.77511465912414</v>
       </c>
       <c r="F15" t="n">
-        <v>63.93042542894552</v>
+        <v>63.93042542894548</v>
       </c>
       <c r="G15" t="n">
-        <v>57.9201833596402</v>
+        <v>57.92018335964016</v>
       </c>
       <c r="H15" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I15" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J15" t="n">
-        <v>250.111345930016</v>
+        <v>250.1113459300159</v>
       </c>
       <c r="K15" t="n">
-        <v>565.4996394772296</v>
+        <v>565.4996394772295</v>
       </c>
       <c r="L15" t="n">
         <v>1006.535493996958</v>
@@ -5366,34 +5366,34 @@
         <v>2052.148604861293</v>
       </c>
       <c r="P15" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="R15" t="n">
-        <v>2132.837892265885</v>
+        <v>2132.837892265884</v>
       </c>
       <c r="S15" t="n">
-        <v>1998.594143492788</v>
+        <v>1998.594143492787</v>
       </c>
       <c r="T15" t="n">
         <v>1914.578037974811</v>
       </c>
       <c r="U15" t="n">
-        <v>1510.377607875899</v>
+        <v>1832.599830098121</v>
       </c>
       <c r="V15" t="n">
-        <v>1413.902186470324</v>
+        <v>1413.902186470323</v>
       </c>
       <c r="W15" t="n">
-        <v>1299.38386029878</v>
+        <v>977.1616380765568</v>
       </c>
       <c r="X15" t="n">
-        <v>875.2800830812164</v>
+        <v>875.2800830812158</v>
       </c>
       <c r="Y15" t="n">
-        <v>794.0766560447171</v>
+        <v>471.8544338224942</v>
       </c>
     </row>
     <row r="16">
@@ -5433,16 +5433,16 @@
         <v>1597.292803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1593.954249936398</v>
+        <v>1591.075096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1495.074513298618</v>
+        <v>1492.195360291075</v>
       </c>
       <c r="N16" t="n">
-        <v>1342.63903405416</v>
+        <v>1339.759881046618</v>
       </c>
       <c r="O16" t="n">
-        <v>1112.434307960106</v>
+        <v>1109.555154952564</v>
       </c>
       <c r="P16" t="n">
         <v>821.1153191039225</v>
@@ -5451,10 +5451,10 @@
         <v>466.1433328154396</v>
       </c>
       <c r="R16" t="n">
-        <v>84.48167017509829</v>
+        <v>84.48167017509826</v>
       </c>
       <c r="S16" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="T16" t="n">
         <v>163.0051070276573</v>
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>603.5035534240047</v>
+        <v>608.1266695820785</v>
       </c>
       <c r="C17" t="n">
-        <v>471.7110501482533</v>
+        <v>476.3341663063271</v>
       </c>
       <c r="D17" t="n">
-        <v>379.4492766736576</v>
+        <v>384.0723928317313</v>
       </c>
       <c r="E17" t="n">
-        <v>293.2237316162145</v>
+        <v>297.8468477742883</v>
       </c>
       <c r="F17" t="n">
-        <v>206.466530901051</v>
+        <v>211.0896470591248</v>
       </c>
       <c r="G17" t="n">
-        <v>126.9664193797369</v>
+        <v>126.9664193797368</v>
       </c>
       <c r="H17" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I17" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J17" t="n">
-        <v>141.5959849731395</v>
+        <v>567.5976741934346</v>
       </c>
       <c r="K17" t="n">
-        <v>704.2743052432502</v>
+        <v>1215.057674193435</v>
       </c>
       <c r="L17" t="n">
-        <v>934.771587554808</v>
+        <v>1582.231587554807</v>
       </c>
       <c r="M17" t="n">
-        <v>1582.231587554808</v>
+        <v>2229.691587554807</v>
       </c>
       <c r="N17" t="n">
-        <v>2229.691587554809</v>
+        <v>2229.691587554807</v>
       </c>
       <c r="O17" t="n">
-        <v>2406.244759641281</v>
+        <v>2406.244759641279</v>
       </c>
       <c r="P17" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="Q17" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="R17" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="S17" t="n">
-        <v>2472.335336314594</v>
+        <v>2472.335336314592</v>
       </c>
       <c r="T17" t="n">
-        <v>2208.4796601358</v>
+        <v>2208.479660135798</v>
       </c>
       <c r="U17" t="n">
-        <v>1875.042017309682</v>
+        <v>1875.04201730968</v>
       </c>
       <c r="V17" t="n">
-        <v>1561.051083807839</v>
+        <v>1561.051083807838</v>
       </c>
       <c r="W17" t="n">
-        <v>1238.451613120013</v>
+        <v>1238.451613120012</v>
       </c>
       <c r="X17" t="n">
-        <v>962.409357099137</v>
+        <v>967.0324732572108</v>
       </c>
       <c r="Y17" t="n">
-        <v>768.1493240862012</v>
+        <v>772.772440244275</v>
       </c>
     </row>
     <row r="18">
@@ -5561,34 +5561,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>502.6636970481491</v>
+        <v>1147.108141492593</v>
       </c>
       <c r="C18" t="n">
-        <v>460.1385329617659</v>
+        <v>1104.58297740621</v>
       </c>
       <c r="D18" t="n">
-        <v>430.9085461964097</v>
+        <v>753.130768418632</v>
       </c>
       <c r="E18" t="n">
         <v>406.9973368813464</v>
       </c>
       <c r="F18" t="n">
-        <v>63.93042542894552</v>
+        <v>63.93042542894548</v>
       </c>
       <c r="G18" t="n">
-        <v>57.9201833596402</v>
+        <v>57.92018335964016</v>
       </c>
       <c r="H18" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I18" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J18" t="n">
-        <v>250.111345930016</v>
+        <v>250.1113459300159</v>
       </c>
       <c r="K18" t="n">
-        <v>565.4996394772296</v>
+        <v>565.4996394772295</v>
       </c>
       <c r="L18" t="n">
         <v>1006.535493996958</v>
@@ -5603,34 +5603,34 @@
         <v>2052.148604861293</v>
       </c>
       <c r="P18" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="R18" t="n">
-        <v>2132.837892265885</v>
+        <v>2132.837892265884</v>
       </c>
       <c r="S18" t="n">
-        <v>1998.594143492788</v>
+        <v>1998.594143492787</v>
       </c>
       <c r="T18" t="n">
-        <v>1689.383823065442</v>
+        <v>1914.578037974811</v>
       </c>
       <c r="U18" t="n">
-        <v>1607.405615188752</v>
+        <v>1832.599830098121</v>
       </c>
       <c r="V18" t="n">
-        <v>1188.707971560954</v>
+        <v>1736.124408692545</v>
       </c>
       <c r="W18" t="n">
-        <v>751.9674231671879</v>
+        <v>1621.606082521001</v>
       </c>
       <c r="X18" t="n">
-        <v>650.085868171847</v>
+        <v>1519.72452752566</v>
       </c>
       <c r="Y18" t="n">
-        <v>568.8824411353477</v>
+        <v>1438.521100489161</v>
       </c>
     </row>
     <row r="19">
@@ -5691,7 +5691,7 @@
         <v>81.60251716755613</v>
       </c>
       <c r="S19" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="T19" t="n">
         <v>163.0051070276573</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>603.5035534240047</v>
+        <v>608.1266695820786</v>
       </c>
       <c r="C20" t="n">
-        <v>471.7110501482533</v>
+        <v>476.3341663063272</v>
       </c>
       <c r="D20" t="n">
-        <v>379.4492766736576</v>
+        <v>384.0723928317314</v>
       </c>
       <c r="E20" t="n">
-        <v>293.2237316162145</v>
+        <v>297.8468477742883</v>
       </c>
       <c r="F20" t="n">
         <v>211.0896470591248</v>
@@ -5737,58 +5737,58 @@
         <v>126.9664193797369</v>
       </c>
       <c r="H20" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I20" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J20" t="n">
-        <v>518.4775676050593</v>
+        <v>567.5976741934346</v>
       </c>
       <c r="K20" t="n">
-        <v>704.2743052432502</v>
+        <v>914.0295456019696</v>
       </c>
       <c r="L20" t="n">
-        <v>934.771587554808</v>
+        <v>1144.526827913527</v>
       </c>
       <c r="M20" t="n">
-        <v>1582.231587554808</v>
+        <v>1791.986827913527</v>
       </c>
       <c r="N20" t="n">
-        <v>2229.691587554809</v>
+        <v>1791.986827913527</v>
       </c>
       <c r="O20" t="n">
-        <v>2406.244759641281</v>
+        <v>1968.54</v>
       </c>
       <c r="P20" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="Q20" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="R20" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="S20" t="n">
-        <v>2472.335336314594</v>
+        <v>2476.958452472668</v>
       </c>
       <c r="T20" t="n">
-        <v>2208.4796601358</v>
+        <v>2213.102776293874</v>
       </c>
       <c r="U20" t="n">
-        <v>1875.042017309682</v>
+        <v>1879.665133467756</v>
       </c>
       <c r="V20" t="n">
-        <v>1561.051083807839</v>
+        <v>1565.674199965913</v>
       </c>
       <c r="W20" t="n">
-        <v>1238.451613120013</v>
+        <v>1243.074729278087</v>
       </c>
       <c r="X20" t="n">
-        <v>962.409357099137</v>
+        <v>967.0324732572109</v>
       </c>
       <c r="Y20" t="n">
-        <v>768.1493240862012</v>
+        <v>772.7724402442751</v>
       </c>
     </row>
     <row r="21">
@@ -5798,34 +5798,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>180.4414748259268</v>
+        <v>824.8859192703712</v>
       </c>
       <c r="C21" t="n">
-        <v>137.9163107395436</v>
+        <v>782.3607551839881</v>
       </c>
       <c r="D21" t="n">
-        <v>108.6863239741874</v>
+        <v>753.1307684186319</v>
       </c>
       <c r="E21" t="n">
-        <v>84.77511465912417</v>
+        <v>406.9973368813464</v>
       </c>
       <c r="F21" t="n">
-        <v>63.93042542894552</v>
+        <v>386.1526476511677</v>
       </c>
       <c r="G21" t="n">
-        <v>57.9201833596402</v>
+        <v>57.92018335964018</v>
       </c>
       <c r="H21" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I21" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J21" t="n">
-        <v>250.111345930016</v>
+        <v>250.1113459300159</v>
       </c>
       <c r="K21" t="n">
-        <v>565.4996394772296</v>
+        <v>565.4996394772295</v>
       </c>
       <c r="L21" t="n">
         <v>1006.535493996958</v>
@@ -5840,34 +5840,34 @@
         <v>2052.148604861293</v>
       </c>
       <c r="P21" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="R21" t="n">
-        <v>2132.837892265885</v>
+        <v>2132.837892265884</v>
       </c>
       <c r="S21" t="n">
-        <v>1998.594143492788</v>
+        <v>1773.399928583418</v>
       </c>
       <c r="T21" t="n">
-        <v>1914.578037974811</v>
+        <v>1367.16160084322</v>
       </c>
       <c r="U21" t="n">
-        <v>1510.377607875899</v>
+        <v>1285.18339296653</v>
       </c>
       <c r="V21" t="n">
-        <v>1091.679964248101</v>
+        <v>1188.707971560954</v>
       </c>
       <c r="W21" t="n">
-        <v>654.939415854335</v>
+        <v>1074.18964538941</v>
       </c>
       <c r="X21" t="n">
-        <v>327.8636459496248</v>
+        <v>972.3080903940692</v>
       </c>
       <c r="Y21" t="n">
-        <v>246.6602189131254</v>
+        <v>891.1046633575698</v>
       </c>
     </row>
     <row r="22">
@@ -5910,25 +5910,25 @@
         <v>1591.075096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1495.074513298618</v>
+        <v>1492.195360291076</v>
       </c>
       <c r="N22" t="n">
-        <v>1342.63903405416</v>
+        <v>1339.759881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1112.434307960106</v>
+        <v>1109.555154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>821.1153191039225</v>
+        <v>818.2361660963808</v>
       </c>
       <c r="Q22" t="n">
-        <v>466.1433328154396</v>
+        <v>463.264179807898</v>
       </c>
       <c r="R22" t="n">
-        <v>84.48167017509829</v>
+        <v>81.60251716755653</v>
       </c>
       <c r="S22" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="T22" t="n">
         <v>163.0051070276573</v>
@@ -5956,64 +5956,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>608.1266695820786</v>
+        <v>608.1266695820785</v>
       </c>
       <c r="C23" t="n">
-        <v>476.3341663063272</v>
+        <v>476.3341663063271</v>
       </c>
       <c r="D23" t="n">
-        <v>384.0723928317315</v>
+        <v>384.0723928317313</v>
       </c>
       <c r="E23" t="n">
-        <v>297.8468477742884</v>
+        <v>297.8468477742883</v>
       </c>
       <c r="F23" t="n">
-        <v>211.0896470591249</v>
+        <v>211.0896470591248</v>
       </c>
       <c r="G23" t="n">
-        <v>126.9664193797369</v>
+        <v>126.9664193797368</v>
       </c>
       <c r="H23" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I23" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J23" t="n">
-        <v>567.5976741934346</v>
+        <v>141.5959849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>753.3944118316256</v>
+        <v>789.0559849731395</v>
       </c>
       <c r="L23" t="n">
-        <v>985.9016280297793</v>
+        <v>1436.515984973139</v>
       </c>
       <c r="M23" t="n">
-        <v>1633.36162802978</v>
+        <v>2083.97598497314</v>
       </c>
       <c r="N23" t="n">
-        <v>1633.36162802978</v>
+        <v>2229.691587554807</v>
       </c>
       <c r="O23" t="n">
-        <v>1809.914800116252</v>
+        <v>2406.244759641279</v>
       </c>
       <c r="P23" t="n">
-        <v>2019.670040474973</v>
+        <v>2616</v>
       </c>
       <c r="Q23" t="n">
-        <v>2616.000000000002</v>
+        <v>2616</v>
       </c>
       <c r="R23" t="n">
-        <v>2616.000000000001</v>
+        <v>2616</v>
       </c>
       <c r="S23" t="n">
-        <v>2472.335336314593</v>
+        <v>2472.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2208.479660135799</v>
+        <v>2213.102776293873</v>
       </c>
       <c r="U23" t="n">
-        <v>1875.042017309681</v>
+        <v>1879.665133467755</v>
       </c>
       <c r="V23" t="n">
         <v>1565.674199965913</v>
@@ -6022,10 +6022,10 @@
         <v>1243.074729278087</v>
       </c>
       <c r="X23" t="n">
-        <v>967.0324732572109</v>
+        <v>967.0324732572108</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.7724402442751</v>
+        <v>772.772440244275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,34 +6035,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1372.302356401963</v>
+        <v>405.6356897352957</v>
       </c>
       <c r="C24" t="n">
-        <v>1104.58297740621</v>
+        <v>137.9163107395436</v>
       </c>
       <c r="D24" t="n">
-        <v>753.130768418632</v>
+        <v>108.6863239741874</v>
       </c>
       <c r="E24" t="n">
-        <v>406.9973368813464</v>
+        <v>84.77511465912414</v>
       </c>
       <c r="F24" t="n">
-        <v>63.93042542894551</v>
+        <v>63.93042542894548</v>
       </c>
       <c r="G24" t="n">
-        <v>57.92018335964021</v>
+        <v>57.92018335964016</v>
       </c>
       <c r="H24" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="I24" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="J24" t="n">
-        <v>250.111345930016</v>
+        <v>250.1113459300159</v>
       </c>
       <c r="K24" t="n">
-        <v>565.4996394772296</v>
+        <v>565.4996394772295</v>
       </c>
       <c r="L24" t="n">
         <v>1006.535493996958</v>
@@ -6077,34 +6077,34 @@
         <v>2052.148604861293</v>
       </c>
       <c r="P24" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2313.910605368536</v>
+        <v>2313.910605368535</v>
       </c>
       <c r="R24" t="n">
-        <v>2132.837892265885</v>
+        <v>2132.837892265884</v>
       </c>
       <c r="S24" t="n">
-        <v>1998.594143492788</v>
+        <v>1998.594143492787</v>
       </c>
       <c r="T24" t="n">
         <v>1914.578037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1832.599830098122</v>
+        <v>1832.599830098121</v>
       </c>
       <c r="V24" t="n">
-        <v>1736.124408692546</v>
+        <v>1736.124408692545</v>
       </c>
       <c r="W24" t="n">
-        <v>1621.606082521002</v>
+        <v>1621.606082521001</v>
       </c>
       <c r="X24" t="n">
-        <v>1519.724527525661</v>
+        <v>1197.502305303438</v>
       </c>
       <c r="Y24" t="n">
-        <v>1438.521100489161</v>
+        <v>794.0766560447165</v>
       </c>
     </row>
     <row r="25">
@@ -6159,13 +6159,13 @@
         <v>821.1153191039225</v>
       </c>
       <c r="Q25" t="n">
-        <v>466.1433328154397</v>
+        <v>466.1433328154396</v>
       </c>
       <c r="R25" t="n">
         <v>84.48167017509826</v>
       </c>
       <c r="S25" t="n">
-        <v>52.32000000000004</v>
+        <v>52.32</v>
       </c>
       <c r="T25" t="n">
         <v>163.0051070276573</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>603.5035534240029</v>
+        <v>608.1266695820786</v>
       </c>
       <c r="C26" t="n">
-        <v>471.7110501482515</v>
+        <v>476.3341663063272</v>
       </c>
       <c r="D26" t="n">
-        <v>379.4492766736557</v>
+        <v>384.0723928317314</v>
       </c>
       <c r="E26" t="n">
-        <v>293.2237316162127</v>
+        <v>297.8468477742883</v>
       </c>
       <c r="F26" t="n">
-        <v>206.4665309010492</v>
+        <v>211.0896470591248</v>
       </c>
       <c r="G26" t="n">
-        <v>126.9664193797368</v>
+        <v>126.9664193797369</v>
       </c>
       <c r="H26" t="n">
         <v>52.32</v>
@@ -6220,19 +6220,19 @@
         <v>567.5976741934346</v>
       </c>
       <c r="K26" t="n">
-        <v>965.1595860769404</v>
+        <v>1215.057674193435</v>
       </c>
       <c r="L26" t="n">
-        <v>1195.656868388498</v>
+        <v>1633.361628029778</v>
       </c>
       <c r="M26" t="n">
-        <v>1195.656868388498</v>
+        <v>1633.361628029778</v>
       </c>
       <c r="N26" t="n">
-        <v>1195.656868388498</v>
+        <v>1633.361628029778</v>
       </c>
       <c r="O26" t="n">
-        <v>1372.210040474971</v>
+        <v>1809.91480011625</v>
       </c>
       <c r="P26" t="n">
         <v>2019.670040474971</v>
@@ -6244,25 +6244,25 @@
         <v>2616</v>
       </c>
       <c r="S26" t="n">
-        <v>2472.335336314592</v>
+        <v>2476.958452472668</v>
       </c>
       <c r="T26" t="n">
-        <v>2208.479660135798</v>
+        <v>2213.102776293874</v>
       </c>
       <c r="U26" t="n">
-        <v>1875.04201730968</v>
+        <v>1879.665133467756</v>
       </c>
       <c r="V26" t="n">
-        <v>1561.051083807838</v>
+        <v>1565.674199965913</v>
       </c>
       <c r="W26" t="n">
-        <v>1238.451613120012</v>
+        <v>1243.074729278087</v>
       </c>
       <c r="X26" t="n">
-        <v>962.4093570991351</v>
+        <v>967.0324732572109</v>
       </c>
       <c r="Y26" t="n">
-        <v>768.1493240861994</v>
+        <v>772.7724402442751</v>
       </c>
     </row>
     <row r="27">
@@ -6278,7 +6278,7 @@
         <v>1104.58297740621</v>
       </c>
       <c r="D27" t="n">
-        <v>753.130768418632</v>
+        <v>753.1307684186319</v>
       </c>
       <c r="E27" t="n">
         <v>406.9973368813464</v>
@@ -6287,7 +6287,7 @@
         <v>63.93042542894548</v>
       </c>
       <c r="G27" t="n">
-        <v>57.92018335964016</v>
+        <v>57.92018335964018</v>
       </c>
       <c r="H27" t="n">
         <v>52.32</v>
@@ -6399,7 +6399,7 @@
         <v>466.1433328154396</v>
       </c>
       <c r="R28" t="n">
-        <v>84.48167017509826</v>
+        <v>84.48167017509823</v>
       </c>
       <c r="S28" t="n">
         <v>52.32</v>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608.1266695820786</v>
+        <v>608.1266695820785</v>
       </c>
       <c r="C29" t="n">
-        <v>476.3341663063272</v>
+        <v>476.3341663063271</v>
       </c>
       <c r="D29" t="n">
-        <v>384.0723928317314</v>
+        <v>384.0723928317313</v>
       </c>
       <c r="E29" t="n">
         <v>297.8468477742883</v>
@@ -6445,7 +6445,7 @@
         <v>211.0896470591248</v>
       </c>
       <c r="G29" t="n">
-        <v>126.9664193797369</v>
+        <v>126.9664193797368</v>
       </c>
       <c r="H29" t="n">
         <v>52.32</v>
@@ -6460,16 +6460,16 @@
         <v>753.3944118316256</v>
       </c>
       <c r="L29" t="n">
-        <v>983.8916941431833</v>
+        <v>985.9016280297782</v>
       </c>
       <c r="M29" t="n">
-        <v>983.8916941431834</v>
+        <v>1633.361628029778</v>
       </c>
       <c r="N29" t="n">
-        <v>983.8916941431834</v>
+        <v>1633.361628029778</v>
       </c>
       <c r="O29" t="n">
-        <v>1631.351694143184</v>
+        <v>1809.914800116251</v>
       </c>
       <c r="P29" t="n">
         <v>2019.670040474971</v>
@@ -6487,7 +6487,7 @@
         <v>2208.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.665133467756</v>
+        <v>1875.04201730968</v>
       </c>
       <c r="V29" t="n">
         <v>1565.674199965913</v>
@@ -6496,10 +6496,10 @@
         <v>1243.074729278087</v>
       </c>
       <c r="X29" t="n">
-        <v>967.0324732572109</v>
+        <v>967.0324732572108</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.7724402442751</v>
+        <v>772.772440244275</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>180.4414748259267</v>
+        <v>1372.302356401962</v>
       </c>
       <c r="C30" t="n">
-        <v>137.9163107395436</v>
+        <v>1104.58297740621</v>
       </c>
       <c r="D30" t="n">
-        <v>108.6863239741874</v>
+        <v>753.130768418632</v>
       </c>
       <c r="E30" t="n">
-        <v>84.77511465912413</v>
+        <v>406.9973368813464</v>
       </c>
       <c r="F30" t="n">
         <v>63.93042542894548</v>
       </c>
       <c r="G30" t="n">
-        <v>57.92018335964018</v>
+        <v>57.92018335964016</v>
       </c>
       <c r="H30" t="n">
         <v>52.32</v>
@@ -6566,19 +6566,19 @@
         <v>1914.578037974811</v>
       </c>
       <c r="U30" t="n">
-        <v>1607.405615188752</v>
+        <v>1832.599830098121</v>
       </c>
       <c r="V30" t="n">
-        <v>1188.707971560954</v>
+        <v>1736.124408692545</v>
       </c>
       <c r="W30" t="n">
-        <v>751.9674231671879</v>
+        <v>1621.606082521001</v>
       </c>
       <c r="X30" t="n">
-        <v>327.8636459496247</v>
+        <v>1519.72452752566</v>
       </c>
       <c r="Y30" t="n">
-        <v>246.6602189131253</v>
+        <v>1438.521100489161</v>
       </c>
     </row>
     <row r="31">
@@ -6621,22 +6621,22 @@
         <v>1591.075096928856</v>
       </c>
       <c r="M31" t="n">
-        <v>1492.195360291076</v>
+        <v>1492.195360291075</v>
       </c>
       <c r="N31" t="n">
-        <v>1342.63903405416</v>
+        <v>1339.759881046618</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.434307960106</v>
+        <v>1109.555154952564</v>
       </c>
       <c r="P31" t="n">
-        <v>821.1153191039225</v>
+        <v>818.2361660963803</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.1433328154396</v>
+        <v>463.2641798078975</v>
       </c>
       <c r="R31" t="n">
-        <v>84.48167017509823</v>
+        <v>84.48167017509826</v>
       </c>
       <c r="S31" t="n">
         <v>52.32</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.1266695820786</v>
+        <v>603.5035534240029</v>
       </c>
       <c r="C32" t="n">
-        <v>476.3341663063272</v>
+        <v>471.7110501482515</v>
       </c>
       <c r="D32" t="n">
-        <v>384.0723928317314</v>
+        <v>379.4492766736557</v>
       </c>
       <c r="E32" t="n">
-        <v>297.8468477742883</v>
+        <v>293.2237316162127</v>
       </c>
       <c r="F32" t="n">
-        <v>211.0896470591248</v>
+        <v>206.4665309010492</v>
       </c>
       <c r="G32" t="n">
         <v>126.9664193797369</v>
@@ -6727,16 +6727,16 @@
         <v>1875.04201730968</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.674199965913</v>
+        <v>1561.051083807838</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.074729278087</v>
+        <v>1238.451613120012</v>
       </c>
       <c r="X32" t="n">
-        <v>967.0324732572109</v>
+        <v>962.4093570991351</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.7724402442751</v>
+        <v>768.1493240861994</v>
       </c>
     </row>
     <row r="33">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>405.6356897352957</v>
+        <v>180.4414748259267</v>
       </c>
       <c r="C33" t="n">
         <v>137.9163107395436</v>
@@ -6806,16 +6806,16 @@
         <v>1832.599830098121</v>
       </c>
       <c r="V33" t="n">
-        <v>1736.124408692545</v>
+        <v>1510.930193783176</v>
       </c>
       <c r="W33" t="n">
-        <v>1299.383860298779</v>
+        <v>1074.18964538941</v>
       </c>
       <c r="X33" t="n">
-        <v>1197.502305303438</v>
+        <v>650.0858681718469</v>
       </c>
       <c r="Y33" t="n">
-        <v>794.0766560447165</v>
+        <v>246.6602189131253</v>
       </c>
     </row>
     <row r="34">
@@ -6931,34 +6931,34 @@
         <v>119.1959849731395</v>
       </c>
       <c r="K35" t="n">
-        <v>369.1715875548226</v>
+        <v>489.4559849731395</v>
       </c>
       <c r="L35" t="n">
-        <v>739.4315875548225</v>
+        <v>859.7159849731394</v>
       </c>
       <c r="M35" t="n">
-        <v>1109.691587554823</v>
+        <v>859.7159849731395</v>
       </c>
       <c r="N35" t="n">
-        <v>1109.691587554823</v>
+        <v>859.7159849731395</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.244759641295</v>
+        <v>1036.269157059612</v>
       </c>
       <c r="P35" t="n">
-        <v>1496.000000000016</v>
+        <v>1246.024397418332</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000016</v>
+        <v>1496</v>
       </c>
       <c r="R35" t="n">
         <v>1496</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.123215102471</v>
+        <v>1434.457487638385</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711555</v>
+        <v>1249.38969024747</v>
       </c>
       <c r="U35" t="n">
         <v>994.7399262092307</v>
@@ -6983,43 +6983,43 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>221.786275057013</v>
+        <v>1177.869556492926</v>
       </c>
       <c r="C36" t="n">
-        <v>221.786275057013</v>
+        <v>1177.869556492926</v>
       </c>
       <c r="D36" t="n">
-        <v>221.786275057013</v>
+        <v>826.4173475053474</v>
       </c>
       <c r="E36" t="n">
-        <v>221.786275057013</v>
+        <v>480.2839159680619</v>
       </c>
       <c r="F36" t="n">
-        <v>221.786275057013</v>
+        <v>137.217004515661</v>
       </c>
       <c r="G36" t="n">
-        <v>221.786275057013</v>
+        <v>29.92</v>
       </c>
       <c r="H36" t="n">
-        <v>221.786275057013</v>
+        <v>29.92</v>
       </c>
       <c r="I36" t="n">
         <v>29.92</v>
       </c>
       <c r="J36" t="n">
-        <v>227.711345930016</v>
+        <v>29.92</v>
       </c>
       <c r="K36" t="n">
-        <v>543.0996394772296</v>
+        <v>345.3082935472136</v>
       </c>
       <c r="L36" t="n">
-        <v>904.0158679168098</v>
+        <v>715.5682935472137</v>
       </c>
       <c r="M36" t="n">
-        <v>1188.111259659669</v>
+        <v>715.5682935472137</v>
       </c>
       <c r="N36" t="n">
-        <v>1188.111259659669</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="O36" t="n">
         <v>1234.237999492757</v>
@@ -7034,25 +7034,25 @@
         <v>1320.671196754497</v>
       </c>
       <c r="S36" t="n">
-        <v>1057.043825910204</v>
+        <v>1265.215326769279</v>
       </c>
       <c r="T36" t="n">
-        <v>679.2660481324261</v>
+        <v>1259.987100039182</v>
       </c>
       <c r="U36" t="n">
-        <v>676.0757190436154</v>
+        <v>1256.796770950371</v>
       </c>
       <c r="V36" t="n">
-        <v>658.3881764259183</v>
+        <v>1239.109228332674</v>
       </c>
       <c r="W36" t="n">
-        <v>622.6577290422532</v>
+        <v>1203.378780949008</v>
       </c>
       <c r="X36" t="n">
-        <v>599.564052834791</v>
+        <v>1180.285104741546</v>
       </c>
       <c r="Y36" t="n">
-        <v>221.786275057013</v>
+        <v>1177.869556492926</v>
       </c>
     </row>
     <row r="37">
@@ -7062,22 +7062,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>935.0016858549086</v>
+        <v>507.1403841043793</v>
       </c>
       <c r="C37" t="n">
-        <v>1055.259969496329</v>
+        <v>630.1723899228151</v>
       </c>
       <c r="D37" t="n">
-        <v>1055.259969496329</v>
+        <v>630.1723899228151</v>
       </c>
       <c r="E37" t="n">
-        <v>1055.259969496329</v>
+        <v>630.1723899228151</v>
       </c>
       <c r="F37" t="n">
-        <v>1055.259969496329</v>
+        <v>751.5633625147506</v>
       </c>
       <c r="G37" t="n">
-        <v>1055.259969496329</v>
+        <v>902.6551136475375</v>
       </c>
       <c r="H37" t="n">
         <v>1055.259969496329</v>
@@ -7113,25 +7113,25 @@
         <v>29.92</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="T37" t="n">
-        <v>217.8251070276573</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="U37" t="n">
-        <v>461.4420370429931</v>
+        <v>507.1403841043793</v>
       </c>
       <c r="V37" t="n">
-        <v>657.2934299289391</v>
+        <v>507.1403841043793</v>
       </c>
       <c r="W37" t="n">
-        <v>826.2143481886164</v>
+        <v>507.1403841043793</v>
       </c>
       <c r="X37" t="n">
-        <v>826.2143481886164</v>
+        <v>507.1403841043793</v>
       </c>
       <c r="Y37" t="n">
-        <v>826.2143481886164</v>
+        <v>507.1403841043793</v>
       </c>
     </row>
     <row r="38">
@@ -7171,7 +7171,7 @@
         <v>489.4559849731395</v>
       </c>
       <c r="L38" t="n">
-        <v>859.7159849731394</v>
+        <v>739.431587554807</v>
       </c>
       <c r="M38" t="n">
         <v>1109.691587554807</v>
@@ -7192,19 +7192,19 @@
         <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>994.7399262092307</v>
+        <v>991.405653673316</v>
       </c>
       <c r="V38" t="n">
-        <v>759.5368714952672</v>
+        <v>756.2025989593525</v>
       </c>
       <c r="W38" t="n">
-        <v>515.7252795953201</v>
+        <v>512.3910070594054</v>
       </c>
       <c r="X38" t="n">
         <v>318.4709023623224</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>719.1203429896864</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="C39" t="n">
-        <v>719.1203429896864</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="D39" t="n">
-        <v>719.1203429896864</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E39" t="n">
         <v>372.9869114524009</v>
@@ -7244,22 +7244,22 @@
         <v>29.92</v>
       </c>
       <c r="J39" t="n">
-        <v>29.92</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K39" t="n">
-        <v>345.3082935472136</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L39" t="n">
-        <v>715.5682935472156</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M39" t="n">
-        <v>999.6636852900749</v>
+        <v>599.927050901758</v>
       </c>
       <c r="N39" t="n">
-        <v>999.6636852900749</v>
+        <v>936.4630493772507</v>
       </c>
       <c r="O39" t="n">
-        <v>1369.923685290077</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P39" t="n">
         <v>1496</v>
@@ -7268,28 +7268,28 @@
         <v>1496</v>
       </c>
       <c r="R39" t="n">
-        <v>1184.24389104382</v>
+        <v>1118.222222222222</v>
       </c>
       <c r="S39" t="n">
-        <v>806.4661132660399</v>
+        <v>1062.766352237004</v>
       </c>
       <c r="T39" t="n">
-        <v>801.237886535942</v>
+        <v>684.9885744592261</v>
       </c>
       <c r="U39" t="n">
-        <v>798.0475574471313</v>
+        <v>681.7982453704154</v>
       </c>
       <c r="V39" t="n">
-        <v>780.3600148294342</v>
+        <v>664.1107027527183</v>
       </c>
       <c r="W39" t="n">
-        <v>744.6295674457691</v>
+        <v>628.3802553690532</v>
       </c>
       <c r="X39" t="n">
-        <v>721.5358912383069</v>
+        <v>605.286579161591</v>
       </c>
       <c r="Y39" t="n">
-        <v>719.1203429896864</v>
+        <v>372.9869114524009</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>395.207429369518</v>
+        <v>541.231710015013</v>
       </c>
       <c r="C40" t="n">
-        <v>518.2394351879537</v>
+        <v>664.2637158334488</v>
       </c>
       <c r="D40" t="n">
-        <v>628.5885793129538</v>
+        <v>774.6128599584489</v>
       </c>
       <c r="E40" t="n">
-        <v>628.5885793129538</v>
+        <v>774.6128599584489</v>
       </c>
       <c r="F40" t="n">
-        <v>749.9795519048893</v>
+        <v>774.6128599584489</v>
       </c>
       <c r="G40" t="n">
-        <v>901.0713030376762</v>
+        <v>925.7046110912358</v>
       </c>
       <c r="H40" t="n">
-        <v>901.0713030376762</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="I40" t="n">
-        <v>901.0713030376762</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="J40" t="n">
-        <v>912.4766405753734</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="K40" t="n">
         <v>1066.665307034026</v>
@@ -7350,25 +7350,25 @@
         <v>29.92</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="T40" t="n">
-        <v>29.92</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="U40" t="n">
-        <v>29.92</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="V40" t="n">
-        <v>29.92</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="W40" t="n">
-        <v>29.92</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="X40" t="n">
-        <v>177.9807910241935</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="Y40" t="n">
-        <v>286.4200917032258</v>
+        <v>432.4443723487209</v>
       </c>
     </row>
     <row r="41">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92</v>
+        <v>187.9751295383777</v>
       </c>
       <c r="C41" t="n">
         <v>29.92</v>
@@ -7405,16 +7405,16 @@
         <v>119.1959849731395</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113305</v>
+        <v>489.4559849731395</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228883</v>
+        <v>859.7159849731394</v>
       </c>
       <c r="M41" t="n">
-        <v>905.7500049228921</v>
+        <v>915.9847596412797</v>
       </c>
       <c r="N41" t="n">
-        <v>1109.691587554807</v>
+        <v>915.9847596412797</v>
       </c>
       <c r="O41" t="n">
         <v>1286.24475964128</v>
@@ -7429,25 +7429,25 @@
         <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1368.854228245085</v>
+        <v>1496</v>
       </c>
       <c r="T41" t="n">
-        <v>1078.735925803665</v>
+        <v>1496</v>
       </c>
       <c r="U41" t="n">
-        <v>719.0356567149207</v>
+        <v>1179.395668536801</v>
       </c>
       <c r="V41" t="n">
-        <v>378.7820969504521</v>
+        <v>839.1421087723326</v>
       </c>
       <c r="W41" t="n">
-        <v>29.92</v>
+        <v>490.2800118218805</v>
       </c>
       <c r="X41" t="n">
-        <v>29.92</v>
+        <v>187.9751295383777</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92</v>
+        <v>187.9751295383777</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>318.0281146697906</v>
+        <v>318.0281146697905</v>
       </c>
       <c r="C42" t="n">
-        <v>249.2403243207812</v>
+        <v>249.240324320781</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246924</v>
+        <v>193.7477112927986</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470029</v>
+        <v>143.5738757151091</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419802</v>
+        <v>96.46656022230415</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226644</v>
+        <v>64.19369189037258</v>
       </c>
       <c r="H42" t="n">
         <v>29.92</v>
@@ -7481,19 +7481,19 @@
         <v>29.92</v>
       </c>
       <c r="J42" t="n">
-        <v>227.711345930016</v>
+        <v>29.92</v>
       </c>
       <c r="K42" t="n">
-        <v>510.6524580167888</v>
+        <v>345.3082935472136</v>
       </c>
       <c r="L42" t="n">
-        <v>567.4798694413171</v>
+        <v>715.5682935472137</v>
       </c>
       <c r="M42" t="n">
-        <v>851.5752611841763</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259659669</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="O42" t="n">
         <v>1234.237999492757</v>
@@ -7511,22 +7511,22 @@
         <v>1128.158285598999</v>
       </c>
       <c r="T42" t="n">
-        <v>1017.879553818397</v>
+        <v>1017.879553818396</v>
       </c>
       <c r="U42" t="n">
-        <v>909.6387196790807</v>
+        <v>909.6387196790806</v>
       </c>
       <c r="V42" t="n">
-        <v>786.9006720108786</v>
+        <v>786.9006720108785</v>
       </c>
       <c r="W42" t="n">
-        <v>646.1197195767083</v>
+        <v>646.1197195767082</v>
       </c>
       <c r="X42" t="n">
-        <v>517.9755383187411</v>
+        <v>517.975538318741</v>
       </c>
       <c r="Y42" t="n">
-        <v>410.5094850196155</v>
+        <v>410.5094850196153</v>
       </c>
     </row>
     <row r="43">
@@ -7572,19 +7572,19 @@
         <v>1005.430107765823</v>
       </c>
       <c r="N43" t="n">
-        <v>826.7320022587397</v>
+        <v>826.7320022587398</v>
       </c>
       <c r="O43" t="n">
-        <v>570.2646499020595</v>
+        <v>826.7320022587398</v>
       </c>
       <c r="P43" t="n">
-        <v>252.6830347832496</v>
+        <v>509.1503871399299</v>
       </c>
       <c r="Q43" t="n">
-        <v>29.92</v>
+        <v>131.3726093621521</v>
       </c>
       <c r="R43" t="n">
-        <v>29.92</v>
+        <v>88.34429643772452</v>
       </c>
       <c r="S43" t="n">
         <v>29.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29.92</v>
+        <v>277.2567842483007</v>
       </c>
       <c r="C44" t="n">
-        <v>29.92</v>
+        <v>277.2567842483007</v>
       </c>
       <c r="D44" t="n">
-        <v>29.92</v>
+        <v>158.7323845110787</v>
       </c>
       <c r="E44" t="n">
-        <v>29.92</v>
+        <v>46.24421319100931</v>
       </c>
       <c r="F44" t="n">
-        <v>29.92</v>
+        <v>46.24421319100931</v>
       </c>
       <c r="G44" t="n">
-        <v>29.92</v>
+        <v>46.24421319100931</v>
       </c>
       <c r="H44" t="n">
         <v>29.92</v>
@@ -7639,19 +7639,19 @@
         <v>29.92</v>
       </c>
       <c r="J44" t="n">
-        <v>400.1800000000038</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K44" t="n">
-        <v>585.9767376381947</v>
+        <v>489.4559849731395</v>
       </c>
       <c r="L44" t="n">
-        <v>915.9847596412759</v>
+        <v>859.7159849731394</v>
       </c>
       <c r="M44" t="n">
-        <v>915.9847596412759</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="N44" t="n">
-        <v>915.9847596412759</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O44" t="n">
         <v>1286.24475964128</v>
@@ -7666,25 +7666,25 @@
         <v>1496</v>
       </c>
       <c r="S44" t="n">
-        <v>1496</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="T44" t="n">
-        <v>1381.040808087168</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="U44" t="n">
-        <v>1021.340538998424</v>
+        <v>966.3724409632214</v>
       </c>
       <c r="V44" t="n">
-        <v>681.0869792339549</v>
+        <v>626.1188811987528</v>
       </c>
       <c r="W44" t="n">
-        <v>332.2248822835028</v>
+        <v>277.2567842483007</v>
       </c>
       <c r="X44" t="n">
-        <v>29.92</v>
+        <v>277.2567842483007</v>
       </c>
       <c r="Y44" t="n">
-        <v>29.92</v>
+        <v>277.2567842483007</v>
       </c>
     </row>
     <row r="45">
@@ -7718,22 +7718,22 @@
         <v>29.92</v>
       </c>
       <c r="J45" t="n">
-        <v>29.92</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K45" t="n">
-        <v>52.38685509283023</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L45" t="n">
-        <v>422.646855092834</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="M45" t="n">
-        <v>706.7422468356932</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="N45" t="n">
-        <v>1043.278245311186</v>
+        <v>863.9779994927574</v>
       </c>
       <c r="O45" t="n">
-        <v>1413.53824531119</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P45" t="n">
         <v>1496</v>
@@ -7806,16 +7806,16 @@
         <v>1163.052803794637</v>
       </c>
       <c r="M46" t="n">
-        <v>1037.910440894231</v>
+        <v>1160.444850760351</v>
       </c>
       <c r="N46" t="n">
-        <v>859.2123353871472</v>
+        <v>981.7467452532678</v>
       </c>
       <c r="O46" t="n">
-        <v>602.744983030467</v>
+        <v>725.2793928965878</v>
       </c>
       <c r="P46" t="n">
-        <v>285.1633679116571</v>
+        <v>407.6977777777778</v>
       </c>
       <c r="Q46" t="n">
         <v>29.92</v>
@@ -7967,25 +7967,25 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>320.8400703517588</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="L2" t="n">
-        <v>308.2909949748743</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>771.5115057379198</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>501.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>226.7515799393686</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>373.2405037325277</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>320.8400703517588</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>308.2909949748744</v>
+        <v>235.5012052109776</v>
       </c>
       <c r="M5" t="n">
         <v>472.2608914614128</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>427.7924845336406</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8292,7 +8292,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N6" t="n">
-        <v>484.6953651829303</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O6" t="n">
         <v>382.6817988009037</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>372.8993027275026</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>320.3286984924623</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>307.6565929648241</v>
+        <v>234.2887077235403</v>
       </c>
       <c r="M8" t="n">
         <v>471.5549969890509</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>426.7802634281129</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8529,7 +8529,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
-        <v>481.6508651829305</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
         <v>382.6817988009037</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>466.326527638191</v>
       </c>
       <c r="L11" t="n">
-        <v>380.6884673049694</v>
+        <v>138.0572030806209</v>
       </c>
       <c r="M11" t="n">
-        <v>939.1988562855338</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N11" t="n">
-        <v>867.9937721401875</v>
+        <v>867.993772140187</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,19 +8915,19 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>466.326527638191</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>421.1744623115578</v>
       </c>
       <c r="M14" t="n">
-        <v>939.1988562855338</v>
+        <v>939.1988562855336</v>
       </c>
       <c r="N14" t="n">
-        <v>867.9937721401875</v>
+        <v>361.1812494954063</v>
       </c>
       <c r="O14" t="n">
-        <v>380.6884673049692</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>380.6884673049695</v>
+        <v>466.326527638191</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>138.0572030806209</v>
       </c>
       <c r="M17" t="n">
-        <v>939.1988562855338</v>
+        <v>939.1988562855336</v>
       </c>
       <c r="N17" t="n">
-        <v>867.9937721401875</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>380.6884673049695</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>162.2577108791355</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>939.1988562855338</v>
+        <v>939.1988562855336</v>
       </c>
       <c r="N20" t="n">
-        <v>867.9937721401875</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>442.1260198396765</v>
       </c>
       <c r="Q20" t="n">
         <v>13.49857879984722</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>466.326527638191</v>
       </c>
       <c r="L23" t="n">
-        <v>2.030236249086784</v>
+        <v>421.1744623115578</v>
       </c>
       <c r="M23" t="n">
-        <v>939.1988562855338</v>
+        <v>939.1988562855336</v>
       </c>
       <c r="N23" t="n">
-        <v>213.993772140187</v>
+        <v>361.1812494954063</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>213.9042164094091</v>
+        <v>466.326527638191</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>189.7037086108944</v>
       </c>
       <c r="M26" t="n">
         <v>285.1988562855334</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>442.1260198396766</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10103,19 +10103,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.030236249085647</v>
       </c>
       <c r="M29" t="n">
-        <v>285.1988562855334</v>
+        <v>939.1988562855336</v>
       </c>
       <c r="N29" t="n">
         <v>213.993772140187</v>
       </c>
       <c r="O29" t="n">
-        <v>475.6634625389166</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>180.3667737101691</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>64.82713630655769</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L35" t="n">
-        <v>141.1744623115578</v>
+        <v>141.1744623115577</v>
       </c>
       <c r="M35" t="n">
-        <v>659.1988562855336</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N35" t="n">
         <v>213.993772140187</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.49857879984722</v>
+        <v>265.9991874681983</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,22 +10650,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>307.1604212273252</v>
+        <v>316.5985743186583</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>145.473175175903</v>
+        <v>295.3819690602905</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>327.4073335019309</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10814,10 +10814,10 @@
         <v>186.326527638191</v>
       </c>
       <c r="L38" t="n">
-        <v>141.1744623115577</v>
+        <v>19.67507097990887</v>
       </c>
       <c r="M38" t="n">
-        <v>537.6994649538844</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N38" t="n">
         <v>213.993772140187</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>27.675503614641</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>316.5985743186603</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>327.407333501933</v>
+        <v>254.1901113963821</v>
       </c>
       <c r="P39" t="n">
-        <v>82.09446356042876</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11048,19 +11048,19 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>141.1744623115577</v>
       </c>
       <c r="M41" t="n">
-        <v>659.1988562855372</v>
+        <v>342.0360024149679</v>
       </c>
       <c r="N41" t="n">
-        <v>419.9953707582829</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>195.6634625389165</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K42" t="n">
-        <v>263.1053100948915</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>316.5985743186583</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>334.6385721499908</v>
       </c>
       <c r="N42" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>327.4073335019309</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>283.822237400873</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L44" t="n">
-        <v>100.5158986783065</v>
+        <v>141.1744623115577</v>
       </c>
       <c r="M44" t="n">
-        <v>285.1988562855334</v>
+        <v>537.6994649538844</v>
       </c>
       <c r="N44" t="n">
         <v>213.993772140187</v>
       </c>
       <c r="O44" t="n">
-        <v>195.6634625389204</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>27.675503614641</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>316.5985743186621</v>
+        <v>266.7181298898984</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O45" t="n">
-        <v>327.4073335019348</v>
+        <v>327.4073335019309</v>
       </c>
       <c r="P45" t="n">
-        <v>38.03935242799163</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2.458477865729947e-12</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.082112132174456</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.082112132173293</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.927393539206605</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>4.576884996493447</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>4.57688499649484</v>
       </c>
     </row>
     <row r="12">
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.850361477466563</v>
+        <v>2.850361477466802</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.576884996493106</v>
+        <v>4.576884996494869</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.850361477466802</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.85036147746672</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4.576884996493106</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.576884996494869</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.850361477466734</v>
+        <v>2.850361477466702</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.576884996493121</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.576884996495266</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24125,7 +24125,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.850361477466762</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.850361477466283</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24225,13 +24225,13 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.576884996494584</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>4.576884996493675</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.850361477466563</v>
+        <v>2.850361477466802</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.576884996494869</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.576884996495266</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466802</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4.576884996494698</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>4.57688499649413</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.850361477466578</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -24851,7 +24851,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.850361477466663</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4.57688499649492</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24942,7 +24942,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>4.576884996495039</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.300929810555573</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.300929810555573</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.300929810555573</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25422,7 +25422,7 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.300929810555544</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -25596,7 +25596,7 @@
         <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>117.3391557398498</v>
@@ -25611,7 +25611,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593948</v>
+        <v>99.89995518593946</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>42.35370301118853</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>42.66497824929007</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>218.3174326828064</v>
@@ -25790,19 +25790,19 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>253.9026788331133</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>156.8868619901808</v>
+        <v>3.422266425597968</v>
       </c>
       <c r="R43" t="n">
-        <v>403.845046013938</v>
+        <v>361.2470162187546</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25836,10 +25836,10 @@
         <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>111.8896287080119</v>
@@ -25848,7 +25848,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593948</v>
+        <v>83.73898412684026</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,10 +25881,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>173.4075194233024</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>218.3174326828064</v>
@@ -26021,7 +26021,7 @@
         <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>121.3090657674594</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26033,7 +26033,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>124.7313321930575</v>
+        <v>3.422266425597996</v>
       </c>
       <c r="R46" t="n">
         <v>403.845046013938</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1136857.505849969</v>
+        <v>1137097.864725697</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2175706.831820639</v>
+        <v>2176083.923000087</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3214417.750121311</v>
+        <v>3214960.139274478</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4250666.31423698</v>
+        <v>4251066.350778139</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5289295.371316398</v>
+        <v>5289695.407857557</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6327924.428395814</v>
+        <v>6328324.464936974</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7366553.485475226</v>
+        <v>7366953.522016387</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8405182.542554639</v>
+        <v>8405582.579095799</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9443811.599634051</v>
+        <v>9444211.636175212</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10482440.65671347</v>
+        <v>10482840.69325462</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11521069.71379288</v>
+        <v>11521469.75033404</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12523142.45162249</v>
+        <v>12523542.48816365</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13561911.73783623</v>
+        <v>13562311.77437739</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14493087.02915566</v>
+        <v>14493487.06569682</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15424262.32047509</v>
+        <v>15424662.35701624</v>
       </c>
     </row>
   </sheetData>
@@ -26269,40 +26269,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1164770.456391358</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="C2" t="n">
-        <v>1164770.456391358</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="D2" t="n">
-        <v>1164781.848321359</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="E2" t="n">
+        <v>1164523.488240559</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1164523.488240559</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1164523.488240558</v>
+      </c>
+      <c r="H2" t="n">
         <v>1164523.488240557</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>1164523.488240558</v>
       </c>
-      <c r="G2" t="n">
-        <v>1164523.488240559</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
+        <v>1164523.488240557</v>
+      </c>
+      <c r="K2" t="n">
         <v>1164523.488240558</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1164523.488240557</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1164523.488240558</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1164523.488240557</v>
       </c>
       <c r="L2" t="n">
         <v>1164523.488240557</v>
       </c>
       <c r="M2" t="n">
-        <v>1164680.714845698</v>
+        <v>1164680.714845699</v>
       </c>
       <c r="N2" t="n">
         <v>1164680.714845699</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230746</v>
+        <v>231098</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>975</v>
       </c>
       <c r="E3" t="n">
-        <v>611512.0000000001</v>
+        <v>611160</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386495.9999999998</v>
+        <v>386848</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>62752.00000000016</v>
+        <v>62400</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602410.774080975</v>
+        <v>602219.8615549036</v>
       </c>
       <c r="C4" t="n">
-        <v>600401.454798864</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598176.9711348976</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>508365.6086022421</v>
+        <v>508171.6422658017</v>
       </c>
       <c r="F4" t="n">
-        <v>506696.9431024051</v>
+        <v>506502.9767659646</v>
       </c>
       <c r="G4" t="n">
-        <v>505025.9749067847</v>
+        <v>504832.0085703442</v>
       </c>
       <c r="H4" t="n">
-        <v>503352.6875026608</v>
+        <v>503158.7211662203</v>
       </c>
       <c r="I4" t="n">
-        <v>501677.0641621618</v>
+        <v>501483.0978257214</v>
       </c>
       <c r="J4" t="n">
-        <v>499999.0879381831</v>
+        <v>499805.1216017427</v>
       </c>
       <c r="K4" t="n">
-        <v>498318.7416602112</v>
+        <v>498124.7753237709</v>
       </c>
       <c r="L4" t="n">
-        <v>496636.0079300366</v>
+        <v>496442.0415935963</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842144</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731495</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523477</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58529.59999999999</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58529.59999999999</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>58551.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74581.81100000003</v>
+        <v>74581.811</v>
       </c>
       <c r="F5" t="n">
-        <v>74581.81100000003</v>
+        <v>74581.811</v>
       </c>
       <c r="G5" t="n">
-        <v>74581.81100000003</v>
+        <v>74581.811</v>
       </c>
       <c r="H5" t="n">
-        <v>74581.81100000003</v>
+        <v>74581.811</v>
       </c>
       <c r="I5" t="n">
-        <v>74581.81100000003</v>
+        <v>74581.811</v>
       </c>
       <c r="J5" t="n">
         <v>74581.811</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>273084.0823103831</v>
+        <v>273015.5007527464</v>
       </c>
       <c r="C6" t="n">
-        <v>505839.4015924941</v>
+        <v>506122.4229402348</v>
       </c>
       <c r="D6" t="n">
-        <v>507078.4771864613</v>
+        <v>507388.2490426056</v>
       </c>
       <c r="E6" t="n">
-        <v>-29935.9313616852</v>
+        <v>-29389.96502524307</v>
       </c>
       <c r="F6" t="n">
-        <v>583244.7341381534</v>
+        <v>583438.700474594</v>
       </c>
       <c r="G6" t="n">
-        <v>584915.702333774</v>
+        <v>585109.668670214</v>
       </c>
       <c r="H6" t="n">
-        <v>586588.9897378976</v>
+        <v>586782.9560743365</v>
       </c>
       <c r="I6" t="n">
-        <v>588264.6130783953</v>
+        <v>588458.5794148371</v>
       </c>
       <c r="J6" t="n">
-        <v>203446.5893023756</v>
+        <v>203288.5556388146</v>
       </c>
       <c r="K6" t="n">
-        <v>591622.935580346</v>
+        <v>591816.9019167875</v>
       </c>
       <c r="L6" t="n">
-        <v>593305.6693105206</v>
+        <v>593499.6356469612</v>
       </c>
       <c r="M6" t="n">
-        <v>515323.0602614838</v>
+        <v>515794.4773652344</v>
       </c>
       <c r="N6" t="n">
-        <v>580042.1909725494</v>
+        <v>580161.6080762995</v>
       </c>
       <c r="O6" t="n">
-        <v>368882.6221849648</v>
+        <v>369002.0392887149</v>
       </c>
       <c r="P6" t="n">
-        <v>542550.3768482101</v>
+        <v>542669.7939519607</v>
       </c>
     </row>
   </sheetData>
@@ -26859,28 +26859,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>654.0000000000005</v>
+        <v>654</v>
       </c>
       <c r="F4" t="n">
-        <v>654.0000000000005</v>
+        <v>654</v>
       </c>
       <c r="G4" t="n">
-        <v>654.0000000000005</v>
+        <v>654</v>
       </c>
       <c r="H4" t="n">
-        <v>654.0000000000005</v>
+        <v>654</v>
       </c>
       <c r="I4" t="n">
-        <v>654.0000000000005</v>
+        <v>654</v>
       </c>
       <c r="J4" t="n">
         <v>654</v>
@@ -26984,7 +26984,7 @@
         <v>319</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27027,7 +27027,7 @@
         <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -27076,22 +27076,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>281.0000000000005</v>
+        <v>280</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>398.201312132171</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711258</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27533,7 +27533,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,19 +27557,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>159.6519859716246</v>
+      </c>
+      <c r="S3" t="n">
+        <v>88.48881128536601</v>
+      </c>
+      <c r="T3" t="n">
+        <v>125.8246912904714</v>
+      </c>
+      <c r="U3" t="n">
         <v>400</v>
-      </c>
-      <c r="S3" t="n">
-        <v>334.3489468037266</v>
-      </c>
-      <c r="T3" t="n">
-        <v>31.47344446279683</v>
-      </c>
-      <c r="U3" t="n">
-        <v>27.1959257979226</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,16 +27594,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>344.8791148384518</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27612,10 +27612,10 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>395.2647849014816</v>
+        <v>249.4250059567768</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
         <v>330.0491815260438</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>362.2230871146351</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>89.48881128536587</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>92.53013679563162</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27834,7 +27834,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>347.6775194675577</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27852,13 +27852,13 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>395.2647849014817</v>
+        <v>396.2647849014815</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>227.7495659428288</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
         <v>150.9483584875727</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946277</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>289.9468508752998</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>160.5184388018129</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>294.7263142651811</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28071,22 +28071,22 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>294.3826718271959</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.047816275856</v>
+        <v>347.9132149025658</v>
       </c>
       <c r="J10" t="n">
         <v>22.13729309820286</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28223,19 +28223,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>96.05772723972478</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>96.05772723972447</v>
+        <v>319</v>
       </c>
       <c r="G12" t="n">
         <v>319</v>
@@ -28271,7 +28271,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
@@ -28283,7 +28283,7 @@
         <v>319</v>
       </c>
       <c r="V12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>319</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.05772723972427</v>
+        <v>96.05772723972478</v>
       </c>
       <c r="C15" t="n">
         <v>319</v>
@@ -28469,7 +28469,7 @@
         <v>319</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F15" t="n">
         <v>319</v>
@@ -28517,19 +28517,19 @@
         <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>319</v>
+        <v>96.05772723972473</v>
       </c>
       <c r="C18" t="n">
         <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -28751,16 +28751,16 @@
         <v>319</v>
       </c>
       <c r="T18" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="U18" t="n">
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X18" t="n">
         <v>319</v>
@@ -28943,13 +28943,13 @@
         <v>319</v>
       </c>
       <c r="E21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>319</v>
       </c>
       <c r="G21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>319</v>
@@ -28985,22 +28985,22 @@
         <v>319</v>
       </c>
       <c r="S21" t="n">
-        <v>319</v>
+        <v>96.05772723972467</v>
       </c>
       <c r="T21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X21" t="n">
-        <v>96.05772723972439</v>
+        <v>319</v>
       </c>
       <c r="Y21" t="n">
         <v>319</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>96.05772723972427</v>
+        <v>96.05772723972473</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29237,10 +29237,10 @@
         <v>319</v>
       </c>
       <c r="X24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29648,16 +29648,16 @@
         <v>319</v>
       </c>
       <c r="C30" t="n">
-        <v>319</v>
+        <v>96.05772723972473</v>
       </c>
       <c r="D30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29702,16 +29702,16 @@
         <v>319</v>
       </c>
       <c r="U30" t="n">
-        <v>96.05772723972478</v>
+        <v>319</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y30" t="n">
         <v>319</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C33" t="n">
-        <v>96.05772723972473</v>
+        <v>319</v>
       </c>
       <c r="D33" t="n">
         <v>319</v>
@@ -29942,13 +29942,13 @@
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>319</v>
+        <v>96.05772723972467</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>158.2009556121982</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S35" t="n">
         <v>397</v>
@@ -30125,22 +30125,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9501396486123</v>
+        <v>218.7261051781079</v>
       </c>
       <c r="H36" t="n">
         <v>324.5441815260438</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30170,10 +30170,10 @@
         <v>397</v>
       </c>
       <c r="S36" t="n">
-        <v>190.9102141495156</v>
+        <v>397</v>
       </c>
       <c r="T36" t="n">
-        <v>28.17594446279664</v>
+        <v>397</v>
       </c>
       <c r="U36" t="n">
         <v>397</v>
@@ -30188,7 +30188,7 @@
         <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.3913927661342</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37">
@@ -30198,10 +30198,10 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C37" t="n">
         <v>397</v>
-      </c>
-      <c r="C37" t="n">
-        <v>394.1982604272574</v>
       </c>
       <c r="D37" t="n">
         <v>285.5362180555555</v>
@@ -30210,13 +30210,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G37" t="n">
-        <v>244.3820695628415</v>
+        <v>397</v>
       </c>
       <c r="H37" t="n">
-        <v>222.8870933147334</v>
+        <v>377.0334123539169</v>
       </c>
       <c r="I37" t="n">
         <v>156.7312261119215</v>
@@ -30249,7 +30249,7 @@
         <v>397</v>
       </c>
       <c r="S37" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T37" t="n">
         <v>397</v>
@@ -30258,10 +30258,10 @@
         <v>397</v>
       </c>
       <c r="V37" t="n">
-        <v>397</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>397</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30404,13 +30404,13 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>189.6234381050061</v>
+        <v>124.2619859716246</v>
       </c>
       <c r="S39" t="n">
-        <v>77.90131128536406</v>
+        <v>397</v>
       </c>
       <c r="T39" t="n">
-        <v>397</v>
+        <v>28.17594446279683</v>
       </c>
       <c r="U39" t="n">
         <v>397</v>
@@ -30425,7 +30425,7 @@
         <v>397</v>
       </c>
       <c r="Y39" t="n">
-        <v>397</v>
+        <v>169.4147217340362</v>
       </c>
     </row>
     <row r="40">
@@ -30447,13 +30447,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>397</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
         <v>397</v>
       </c>
       <c r="H40" t="n">
-        <v>222.8870933147334</v>
+        <v>353.7510917037165</v>
       </c>
       <c r="I40" t="n">
         <v>156.7312261119215</v>
@@ -30462,7 +30462,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>367.377393340435</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L40" t="n">
         <v>325.1555297971234</v>
@@ -30486,10 +30486,10 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T40" t="n">
-        <v>207.1968615882249</v>
+        <v>397</v>
       </c>
       <c r="U40" t="n">
         <v>150.9222929138022</v>
@@ -30498,13 +30498,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X40" t="n">
-        <v>397</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30599,7 +30599,7 @@
         <v>293</v>
       </c>
       <c r="D42" t="n">
-        <v>290.6132265545748</v>
+        <v>293</v>
       </c>
       <c r="E42" t="n">
         <v>293</v>
@@ -30611,7 +30611,7 @@
         <v>293</v>
       </c>
       <c r="H42" t="n">
-        <v>293</v>
+        <v>290.6132265545749</v>
       </c>
       <c r="I42" t="n">
         <v>189.9476123064429</v>
@@ -34746,25 +34746,25 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="L2" t="n">
-        <v>372.9999999999999</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>299.2506142765071</v>
+        <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,7 +34822,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.2235763247276</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K3" t="n">
         <v>226.5315338860743</v>
@@ -34880,16 +34880,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>59.34289678289625</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>155.1400615846995</v>
@@ -34898,10 +34898,10 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>227.1602210552952</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>373.0000000000002</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>373</v>
+        <v>300.2102102361032</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>299.250614276507</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35071,7 +35071,7 @@
         <v>142.5400421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>190.9746900070274</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O6" t="n">
         <v>293.6569652989728</v>
@@ -35120,7 +35120,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>62.14130141200219</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35138,13 +35138,13 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>373.0000000000002</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>18.51090107591537</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>373.0000000000002</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>373</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>373</v>
+        <v>299.6321147587162</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35238,10 +35238,10 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>298.6725187991199</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
-        <v>1.607692654649116e-12</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -35308,7 +35308,7 @@
         <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>188.4896145353295</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
         <v>294.1687294499162</v>
@@ -35357,22 +35357,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>8.846453771640441</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>176.8653986267098</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K11" t="n">
-        <v>187.6734723618091</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>613.5140049934116</v>
+        <v>370.882740769063</v>
       </c>
       <c r="M11" t="n">
-        <v>654.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>654.0000000000003</v>
+        <v>654</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35615,7 +35615,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K13" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35694,19 +35694,19 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
-        <v>187.6734723618091</v>
+        <v>654</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8255376884422</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>654.0000000000003</v>
+        <v>654</v>
       </c>
       <c r="N14" t="n">
-        <v>654.0000000000003</v>
+        <v>147.1874773552193</v>
       </c>
       <c r="O14" t="n">
-        <v>559.0250047660526</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
         <v>211.8739801603236</v>
@@ -35843,7 +35843,7 @@
         <v>74.61793043715849</v>
       </c>
       <c r="H16" t="n">
-        <v>96.11290668526664</v>
+        <v>96.11290668526661</v>
       </c>
       <c r="I16" t="n">
         <v>162.2687738880785</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K17" t="n">
-        <v>568.3619396667785</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>232.8255376884422</v>
+        <v>370.882740769063</v>
       </c>
       <c r="M17" t="n">
-        <v>654.0000000000003</v>
+        <v>654</v>
       </c>
       <c r="N17" t="n">
-        <v>654.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>470.8662299041003</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>187.673472361809</v>
+        <v>349.9311832409445</v>
       </c>
       <c r="L20" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
-        <v>654.0000000000003</v>
+        <v>654</v>
       </c>
       <c r="N20" t="n">
-        <v>654.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P20" t="n">
-        <v>211.8739801603236</v>
+        <v>654</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
-        <v>187.6734723618091</v>
+        <v>654</v>
       </c>
       <c r="L23" t="n">
-        <v>234.8557739375291</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>654.0000000000003</v>
+        <v>654</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>147.1874773552193</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36423,7 +36423,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36563,7 +36563,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K25" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36642,10 +36642,10 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K26" t="n">
-        <v>401.577688771218</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884422</v>
+        <v>422.5292462993366</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>178.3365374610834</v>
       </c>
       <c r="P26" t="n">
-        <v>654.0000000000001</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
         <v>602.3534944697265</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36882,19 +36882,19 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L29" t="n">
-        <v>232.8255376884422</v>
+        <v>234.8557739375279</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>654.0000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>654.0000000000001</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P29" t="n">
-        <v>392.2407538704927</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
         <v>602.3534944697265</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37353,13 +37353,13 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K35" t="n">
-        <v>252.5006086683667</v>
+        <v>374</v>
       </c>
       <c r="L35" t="n">
-        <v>374</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>374.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37371,10 +37371,10 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>252.500608668351</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.584725616725557e-11</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -37429,22 +37429,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>364.5618469086669</v>
+        <v>374</v>
       </c>
       <c r="M36" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>149.9087938843876</v>
       </c>
       <c r="O36" t="n">
-        <v>46.59266649806909</v>
+        <v>374</v>
       </c>
       <c r="P36" t="n">
         <v>264.4060611184268</v>
@@ -37484,10 +37484,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>109.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>121.4730137792127</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -37496,13 +37496,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>154.1463190391835</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -37535,7 +37535,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T37" t="n">
         <v>189.8031384117751</v>
@@ -37544,10 +37544,10 @@
         <v>246.0777070861978</v>
       </c>
       <c r="V37" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>170.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -37593,10 +37593,10 @@
         <v>374</v>
       </c>
       <c r="L38" t="n">
-        <v>373.9999999999999</v>
+        <v>252.500608668351</v>
       </c>
       <c r="M38" t="n">
-        <v>252.500608668351</v>
+        <v>374</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K39" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>374.000000000002</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M39" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>374.000000000002</v>
+        <v>300.7827778944511</v>
       </c>
       <c r="P39" t="n">
-        <v>127.3498128383061</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37733,13 +37733,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>122.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>152.6179304371585</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>130.8639983889832</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
         <v>11.52054296737091</v>
       </c>
       <c r="K40" t="n">
-        <v>155.7461277360132</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37772,10 +37772,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>189.8031384117751</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -37784,13 +37784,13 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>149.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37827,19 +37827,19 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K41" t="n">
-        <v>187.673472361809</v>
+        <v>374</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884423</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>374.0000000000038</v>
+        <v>56.83714612943452</v>
       </c>
       <c r="N41" t="n">
-        <v>206.0015986180959</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>178.3365374610834</v>
+        <v>374</v>
       </c>
       <c r="P41" t="n">
         <v>211.8739801603236</v>
@@ -37903,22 +37903,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>285.7991031179524</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L42" t="n">
-        <v>57.40142568134173</v>
+        <v>374</v>
       </c>
       <c r="M42" t="n">
-        <v>286.9650421645043</v>
+        <v>149.9087938843876</v>
       </c>
       <c r="N42" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>374</v>
       </c>
       <c r="P42" t="n">
         <v>264.4060611184268</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880784</v>
+        <v>136.2687738880785</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557824</v>
+        <v>81.36873439557826</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177507</v>
+        <v>85.80313841177508</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>374.0000000000038</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.673472361809</v>
+        <v>374</v>
       </c>
       <c r="L44" t="n">
-        <v>333.3414363667488</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>252.500608668351</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>374.0000000000038</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P44" t="n">
         <v>211.8739801603236</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K45" t="n">
-        <v>22.69379302306083</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>374.0000000000038</v>
+        <v>324.1195555712401</v>
       </c>
       <c r="M45" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>374.0000000000038</v>
+        <v>374</v>
       </c>
       <c r="P45" t="n">
-        <v>83.29470170586897</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
